--- a/reports/devops-jobs-israel-2026-W28.xlsx
+++ b/reports/devops-jobs-israel-2026-W28.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-06T10:56:15</t>
+    <t xml:space="preserve">2026-07-07T09:57:17</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -267,12 +267,24 @@
     <t xml:space="preserve">2026-06-10</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Python, Bash/Shell, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
   </si>
   <si>
@@ -399,9 +411,6 @@
     <t xml:space="preserve">2026-07-05</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Torq</t>
   </si>
   <si>
@@ -495,79 +504,460 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfraEdge IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4433786911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4436979806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435244149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4433783879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4436283605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437766169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexxen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchPointIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-1006977-at-elad-software-systems-4437184121</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA AI</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4432394657</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-datateam-4433916819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
   </si>
   <si>
     <t xml:space="preserve">Jobgether</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobgether-4436041571</t>
   </si>
   <si>
-    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433127155</t>
+    <t xml:space="preserve">Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4437152019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-varonis-4435128191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4432713200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-and-automation-engineer-at-nvidia-ai-4433143928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4M Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
   </si>
   <si>
     <t xml:space="preserve">Senior DevSecOps Engineer - Berlin / Lisbon / Warsaw</t>
@@ -576,802 +966,346 @@
     <t xml:space="preserve">1GLOBAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-berlin-lisbon-warsaw-at-1global-4436088167</t>
   </si>
   <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435227245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4433783879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4437124828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (FinOps oriented)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudTeam.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-finops-oriented-at-cloudteam-ai-4432709751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfraEdge IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4433786911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4437143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - for the Development Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recruitx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afula, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-for-the-development-department-at-recruitx-4437173418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - Naval Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-naval-systems-at-elbit-systems-israel-4423104948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XTEND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4437762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Sela</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4432791201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415730614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINANCIAL INSTITUTION SERVICES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-financial-institution-services-4435534397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס/ת DEVOPS ותמיכת תשתיות מחשוב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-devops-%D7%95%D7%AA%D7%9E%D7%99%D7%9B%D7%AA-%D7%AA%D7%A9%D7%AA%D7%99%D7%95%D7%AA-%D7%9E%D7%97%D7%A9%D7%95%D7%91-at-elad-software-systems-4434494489</t>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, GCP, Cloud (any), Kubernetes, CI/CD, Terraform/IaC, Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4432394818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stampli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-stampli-4427522493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-varonis-4416244206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-sre-at-nebius-4409959205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech Lead DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tech-lead-devops-at-maytronics-4434952849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer | Leading Company (5466)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-leading-company-5466-at-ingima-4436983893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-and-automation-engineer-at-nvidia-ai-4433143928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4436979806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MatchPointIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4437143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4433773897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-system-engineer-at-abra-4436065992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SearchApi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-searchapi-4434496090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4434448757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4431944036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4433922741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-camtek-4432761684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-digital-applications-at-maytronics-4425076264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aspect Imaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-aspect-imaging-4434489230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturing Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manufacturing-infrastructure-engineer-at-quantum-machines-4434304423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kroll Consulting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-kroll-consulting-4437140520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-gotfriends-4433900010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4428923734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+    <t xml:space="preserve">System Administrator (36781)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, GCP, Cloud (any), Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36781-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36792)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36792-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436990743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
@@ -1380,40 +1314,37 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
   </si>
   <si>
     <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3 Support Engineer (Data Center)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-data-center-at-nebius-4429629836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1422,15 +1353,15 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -1438,6 +1369,9 @@
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1589,7 +1523,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1605,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -1613,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>867</v>
+        <v>882</v>
       </c>
     </row>
     <row r="10">
@@ -1685,7 +1619,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -1693,7 +1627,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1712,28 +1646,28 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -1741,7 +1675,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1749,9 +1683,17 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1768,39 +1710,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>466</v>
+        <v>359</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>380</v>
+        <v>443</v>
       </c>
       <c r="B3" s="3">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="B5" s="3">
         <v>25</v>
@@ -1808,31 +1750,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>470</v>
+        <v>355</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>447</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
@@ -1840,23 +1782,23 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -1864,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -1875,23 +1817,23 @@
         <v>325</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>176</v>
+        <v>450</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1916,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2">
@@ -1930,13 +1872,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1945,88 +1887,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>36.8</v>
+        <v>34.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.0</v>
+        <v>8.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>37.5</v>
+        <v>35.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>17.2</v>
+        <v>15.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2037,9 +1979,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2110,7 +2052,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -2142,7 +2084,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -2174,7 +2116,7 @@
         <v>50</v>
       </c>
       <c r="J4" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -2206,7 +2148,7 @@
         <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -2238,7 +2180,7 @@
         <v>40</v>
       </c>
       <c r="J6" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -2270,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="J7" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -2302,7 +2244,7 @@
         <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -2334,7 +2276,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -2366,7 +2308,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -2398,7 +2340,7 @@
         <v>40</v>
       </c>
       <c r="J11" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -2430,7 +2372,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -2447,7 +2389,7 @@
         <v>46</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>84</v>
@@ -2462,12 +2404,12 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>83</v>
@@ -2482,24 +2424,24 @@
         <v>37</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J14" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>83</v>
@@ -2526,7 +2468,7 @@
         <v>93</v>
       </c>
       <c r="J15" s="3">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -2555,15 +2497,15 @@
         <v>96</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>83</v>
@@ -2578,19 +2520,19 @@
         <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J17" s="3">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2598,10 +2540,10 @@
         <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>46</v>
@@ -2610,30 +2552,30 @@
         <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J18" s="3">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>46</v>
@@ -2654,7 +2596,7 @@
         <v>110</v>
       </c>
       <c r="J19" s="3">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -2662,10 +2604,10 @@
         <v>111</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>46</v>
@@ -2674,16 +2616,16 @@
         <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="J20" s="3">
         <v>39</v>
@@ -2691,13 +2633,13 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>46</v>
@@ -2706,83 +2648,83 @@
         <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="J21" s="3">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J22" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="J23" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
@@ -2790,106 +2732,106 @@
         <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J24" s="3">
-        <v>55</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="J25" s="3">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="J26" s="3">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>46</v>
@@ -2898,30 +2840,30 @@
         <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>46</v>
@@ -2930,19 +2872,19 @@
         <v>37</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J28" s="3">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -2950,108 +2892,110 @@
         <v>149</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>46</v>
+        <v>154</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="J30" s="3">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>158</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>160</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D32" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
@@ -3061,15 +3005,15 @@
         <v>163</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>165</v>
@@ -3078,7 +3022,7 @@
         <v>166</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>47</v>
@@ -3091,7 +3035,7 @@
         <v>167</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -3099,29 +3043,29 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -3129,48 +3073,46 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>176</v>
-      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J35" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>47</v>
@@ -3180,56 +3122,54 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>185</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>46</v>
@@ -3242,27 +3182,27 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>47</v>
@@ -3272,57 +3212,57 @@
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>47</v>
@@ -3332,10 +3272,10 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -3343,48 +3283,46 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>200</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J42" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>47</v>
@@ -3394,10 +3332,10 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3405,13 +3343,13 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>46</v>
@@ -3419,31 +3357,29 @@
       <c r="E44" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>193</v>
+        <v>86</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>46</v>
@@ -3451,32 +3387,34 @@
       <c r="E45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J45" s="3">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>47</v>
@@ -3486,57 +3424,57 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="J46" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>217</v>
+        <v>86</v>
       </c>
       <c r="J47" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>47</v>
@@ -3546,24 +3484,24 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>222</v>
+        <v>51</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>46</v>
@@ -3576,54 +3514,54 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="J49" s="3">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>225</v>
+        <v>51</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>46</v>
@@ -3636,54 +3574,54 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="J51" s="3">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="J52" s="3">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>46</v>
@@ -3696,24 +3634,24 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J53" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>46</v>
@@ -3726,40 +3664,40 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J54" s="3">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>51</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J55" s="3">
         <v>46</v>
@@ -3767,32 +3705,32 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>244</v>
+        <v>129</v>
       </c>
       <c r="J56" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3800,13 +3738,13 @@
         <v>51</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>37</v>
@@ -3816,57 +3754,57 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="C58" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J58" s="3">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>251</v>
+        <v>162</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>47</v>
@@ -3876,54 +3814,54 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="J60" s="3">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>46</v>
@@ -3936,24 +3874,24 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>64</v>
+        <v>182</v>
       </c>
       <c r="J61" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>46</v>
@@ -3966,24 +3904,24 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>89</v>
+        <v>228</v>
       </c>
       <c r="J62" s="3">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>46</v>
@@ -3996,24 +3934,24 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="J63" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>46</v>
@@ -4026,24 +3964,24 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>268</v>
+        <v>86</v>
       </c>
       <c r="J64" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>269</v>
+        <v>98</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>270</v>
+        <v>218</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>46</v>
@@ -4056,27 +3994,27 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="J65" s="3">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>274</v>
+        <v>171</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>47</v>
@@ -4086,27 +4024,27 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>276</v>
+        <v>104</v>
       </c>
       <c r="J66" s="3">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>181</v>
+        <v>269</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4116,27 +4054,27 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>278</v>
+        <v>64</v>
       </c>
       <c r="J67" s="3">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>51</v>
+        <v>271</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>281</v>
+        <v>135</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
@@ -4146,119 +4084,119 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>283</v>
+        <v>156</v>
       </c>
       <c r="J68" s="3">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>284</v>
+        <v>51</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>276</v>
+        <v>104</v>
       </c>
       <c r="J69" s="3">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>153</v>
+        <v>281</v>
       </c>
       <c r="J70" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>292</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>47</v>
@@ -4268,114 +4206,116 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>298</v>
+        <v>201</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>299</v>
+        <v>197</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>220</v>
+        <v>135</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="J75" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>46</v>
@@ -4388,10 +4328,10 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="J76" s="3">
         <v>0</v>
@@ -4399,16 +4339,16 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>47</v>
@@ -4418,27 +4358,27 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="J77" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>313</v>
+        <v>166</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
@@ -4448,24 +4388,24 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>158</v>
+        <v>304</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>46</v>
@@ -4478,54 +4418,54 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>126</v>
+        <v>306</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>125</v>
+        <v>294</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>126</v>
+        <v>309</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>46</v>
@@ -4538,13 +4478,13 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="J81" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -4552,10 +4492,10 @@
         <v>51</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>46</v>
@@ -4568,149 +4508,151 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>325</v>
+        <v>205</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>280</v>
+        <v>162</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>281</v>
+        <v>46</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>168</v>
+        <v>322</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F86" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="J86" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>336</v>
+        <v>56</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>132</v>
+        <v>328</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>47</v>
@@ -4720,24 +4662,24 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>340</v>
+        <v>64</v>
       </c>
       <c r="J87" s="3">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>46</v>
@@ -4750,27 +4692,27 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="J88" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>343</v>
+        <v>190</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>47</v>
@@ -4780,13 +4722,13 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="J89" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -4794,13 +4736,13 @@
         <v>336</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>47</v>
@@ -4810,10 +4752,10 @@
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="J90" s="3">
         <v>0</v>
@@ -4821,13 +4763,13 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>349</v>
+        <v>236</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>46</v>
@@ -4840,27 +4782,27 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>100</v>
+        <v>342</v>
       </c>
       <c r="J91" s="3">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>251</v>
+        <v>327</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>132</v>
+        <v>328</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>47</v>
@@ -4870,27 +4812,27 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>299</v>
+        <v>162</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>47</v>
@@ -4900,27 +4842,27 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>355</v>
+        <v>86</v>
       </c>
       <c r="J93" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>358</v>
+        <v>162</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -4930,167 +4872,17 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
       <c r="J94" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J95" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J96" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J98" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J99" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J99"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5185,11 +4977,6 @@
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5197,8 +4984,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5231,32 +5018,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>166</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>167</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5264,18 +5051,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5283,18 +5070,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5302,18 +5089,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5321,18 +5108,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5340,18 +5127,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>251</v>
+        <v>162</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5359,18 +5146,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>294</v>
+        <v>220</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>295</v>
+        <v>197</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5378,18 +5165,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>296</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5397,18 +5184,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>303</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5416,18 +5203,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5435,18 +5222,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5454,18 +5241,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5473,7 +5260,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15">
@@ -5481,10 +5268,10 @@
         <v>336</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5492,18 +5279,18 @@
         <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5511,7 +5298,7 @@
         <v>22</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5545,47 +5332,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>176</v>
+        <v>292</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5601,7 +5388,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5609,15 +5396,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5625,15 +5412,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>156</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5641,23 +5428,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>380</v>
+        <v>159</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5665,7 +5452,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5678,7 +5465,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5687,7 +5474,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
@@ -5695,7 +5482,7 @@
         <v>83</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -5708,15 +5495,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5724,7 +5511,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>223</v>
+        <v>286</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5748,7 +5535,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5756,7 +5543,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5764,7 +5551,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5772,7 +5559,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5780,7 +5567,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5788,7 +5575,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5796,7 +5583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5804,7 +5591,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5818,23 +5605,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
@@ -5845,10 +5632,10 @@
         <v>83</v>
       </c>
       <c r="C2" s="3">
-        <v>19.2</v>
+        <v>26.9</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -5884,7 +5671,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C5" s="3">
         <v>6.7</v>
@@ -5912,7 +5699,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C7" s="3">
         <v>5.3</v>
@@ -5926,7 +5713,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -5940,13 +5727,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5954,13 +5741,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5968,13 +5755,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="C11" s="3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5982,13 +5769,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5996,7 +5783,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C13" s="3">
         <v>2.9</v>
@@ -6010,13 +5797,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>298</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6024,10 +5811,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>307</v>
+        <v>177</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6038,13 +5825,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6064,21 +5851,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3">
@@ -6086,10 +5873,10 @@
         <v>47</v>
       </c>
       <c r="B3" s="3">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
@@ -6097,10 +5884,10 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -6119,7 +5906,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
@@ -6127,15 +5914,15 @@
         <v>46</v>
       </c>
       <c r="B2" s="3">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -6143,28 +5930,28 @@
         <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>123</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>119</v>
+        <v>328</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6172,15 +5959,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>281</v>
+        <v>154</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>151</v>
+        <v>244</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6195,7 +5982,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6207,10 +5994,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6222,10 +6009,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6242,31 +6029,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>310</v>
+        <v>376</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>397</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -6274,31 +6061,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>402</v>
+        <v>201</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>381</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4">
@@ -6306,31 +6093,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>336</v>
+        <v>385</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>215</v>
+        <v>386</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>135</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5">
@@ -6338,31 +6125,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>256</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>174</v>
+        <v>391</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="F5" s="3">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>110</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6">
@@ -6370,31 +6157,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>218</v>
+        <v>286</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>256</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7">
@@ -6402,31 +6189,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>416</v>
+        <v>323</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>223</v>
+        <v>324</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>313</v>
+        <v>175</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="F7" s="3">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>418</v>
+        <v>326</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>419</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -6434,31 +6221,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>158</v>
+        <v>398</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F8" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>419</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
@@ -6466,31 +6253,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="F9" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -6498,31 +6285,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>425</v>
+        <v>333</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>426</v>
+        <v>334</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="F10" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>428</v>
+        <v>335</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>100</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -6530,31 +6317,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>351</v>
+        <v>408</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>251</v>
+        <v>162</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F11" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>161</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12">
@@ -6562,31 +6349,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>432</v>
+        <v>256</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>203</v>
+        <v>391</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="F12" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>244</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13">
@@ -6594,31 +6381,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>437</v>
+        <v>387</v>
       </c>
       <c r="F13" s="3">
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>340</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14">
@@ -6626,31 +6413,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>223</v>
+        <v>324</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>313</v>
+        <v>175</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>256</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15">
@@ -6658,31 +6445,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="F15" s="3">
         <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -6690,31 +6477,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>447</v>
+        <v>397</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>181</v>
+        <v>284</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17">
@@ -6722,31 +6509,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F17" s="3">
         <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18">
@@ -6754,31 +6541,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>61</v>
+        <v>397</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>431</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>63</v>
+        <v>432</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>64</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19">
@@ -6786,31 +6573,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>454</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>455</v>
+        <v>57</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="F19" s="3">
         <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>457</v>
+        <v>63</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -6818,31 +6605,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>266</v>
+        <v>177</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F20" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -6850,31 +6637,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W28.xlsx
+++ b/reports/devops-jobs-israel-2026-W28.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-07T09:57:17</t>
+    <t xml:space="preserve">2026-07-08T08:41:32</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">1.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -267,262 +270,274 @@
     <t xml:space="preserve">2026-06-10</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Python, Bash/Shell, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668075006</t>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Engineer - Billing Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
     <t xml:space="preserve">Dropit</t>
@@ -573,7 +588,16 @@
     <t xml:space="preserve">Nogamy</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4436979806</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4437795960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
   </si>
   <si>
     <t xml:space="preserve">AudioCodes</t>
@@ -582,7 +606,43 @@
     <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435244149</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435227245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
   </si>
   <si>
     <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
@@ -597,6 +657,171 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
   </si>
   <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437766169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer (Linux &amp; AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CloudBuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-linux-aws-at-cloudbuzz-4434817637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4434807946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobgether-4436041571</t>
+  </si>
+  <si>
     <t xml:space="preserve">DataTeam</t>
   </si>
   <si>
@@ -606,772 +831,550 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4433783879</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4436283605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
+    <t xml:space="preserve">Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-1006977-at-elad-software-systems-4437184121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Databricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4378744789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer | Leading Company (5466)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-leading-company-5466-at-ingima-4438178609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4434528681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchPointIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-system-engineer-at-abra-4436065992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vega-In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-vega-in-4433188707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-comblack-4436344599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cyera-4437443238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4436064850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-reliability-engineer-at-silk-4437161833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437766169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4421613319</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Nexxen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nexxen-4415694961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MatchPointIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-1006977-at-elad-software-systems-4437184121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4432394657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobgether-4436041571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4437152019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-varonis-4435128191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4432713200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QA and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/qa-and-automation-engineer-at-nvidia-ai-4433143928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4M Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-4m-analytics-4434993631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer - Berlin / Lisbon / Warsaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1GLOBAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-berlin-lisbon-warsaw-at-1global-4436088167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP &amp; System Administrator (36759)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gcp-system-administrator-36759-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4437143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - for the Development Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recruitx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afula, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-for-the-development-department-at-recruitx-4437173418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - Naval Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-naval-systems-at-elbit-systems-israel-4423104948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XTEND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-xtend-4437762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, GCP, Cloud (any), Kubernetes, CI/CD, Terraform/IaC, Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36781)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, GCP, Cloud (any), Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36781-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36792)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36792-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436990743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1523,7 +1526,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -1531,7 +1534,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1539,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -1547,7 +1550,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>882</v>
+        <v>895</v>
       </c>
     </row>
     <row r="10">
@@ -1555,7 +1558,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1571,7 +1574,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1580,26 +1583,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1608,26 +1611,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1643,15 +1646,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3">
         <v>38</v>
@@ -1659,15 +1662,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -1675,7 +1678,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1683,17 +1686,9 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="B7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1710,130 +1705,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>359</v>
+        <v>445</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>443</v>
+        <v>356</v>
       </c>
       <c r="B3" s="3">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B7" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>354</v>
+        <v>450</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>448</v>
+        <v>350</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>325</v>
+        <v>263</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>450</v>
+        <v>348</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1852,123 +1847,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>13.8</v>
+        <v>12.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>34.3</v>
+        <v>33.4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.6</v>
+        <v>9.2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8</v>
+        <v>3.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.8</v>
+        <v>34.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.6</v>
+        <v>20.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.2</v>
+        <v>15.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1979,9 +1974,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1993,441 +1988,441 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J3" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="3">
         <v>57</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="3">
-        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J11" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J12" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>88</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>89</v>
@@ -2436,71 +2431,71 @@
         <v>90</v>
       </c>
       <c r="J14" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" s="3">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="J16" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2508,564 +2503,562 @@
         <v>98</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>100</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J17" s="3">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J18" s="3">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J19" s="3">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="J20" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J21" s="3">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>124</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>125</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="J23" s="3">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="J25" s="3">
-        <v>56</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="J27" s="3">
-        <v>56</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="J29" s="3">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="J30" s="3">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>159</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -3073,29 +3066,29 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J35" s="3">
         <v>1</v>
@@ -3103,89 +3096,89 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="J37" s="3">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J38" s="3">
         <v>44</v>
@@ -3193,664 +3186,664 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="J39" s="3">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>198</v>
+        <v>47</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>86</v>
+        <v>166</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>46</v>
+        <v>202</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="I45" s="3" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="J45" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="J46" s="3">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>214</v>
+        <v>52</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>93</v>
+        <v>172</v>
       </c>
       <c r="J48" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>51</v>
+        <v>214</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>162</v>
+        <v>216</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="J49" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>51</v>
+        <v>218</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>198</v>
+        <v>47</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="J51" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="J52" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>149</v>
+        <v>227</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
       <c r="J54" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="J55" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>244</v>
+        <v>37</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>246</v>
+        <v>65</v>
       </c>
       <c r="J57" s="3">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>162</v>
+        <v>242</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>129</v>
+        <v>245</v>
       </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="J59" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="J60" s="3">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61">
@@ -3858,328 +3851,330 @@
         <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="J61" s="3">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>46</v>
+        <v>258</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="J62" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="G63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="J63" s="3">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>42</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="J65" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>265</v>
+        <v>127</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="J66" s="3">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="J67" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>273</v>
+        <v>160</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="G68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>156</v>
+        <v>280</v>
       </c>
       <c r="J68" s="3">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>51</v>
+        <v>281</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="J69" s="3">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>166</v>
+        <v>285</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>46</v>
+        <v>202</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>279</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="J71" s="3">
         <v>0</v>
@@ -4187,181 +4182,179 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>269</v>
+        <v>160</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="J72" s="3">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>201</v>
+        <v>294</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>198</v>
+        <v>47</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="J73" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>198</v>
+        <v>47</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>292</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>294</v>
+        <v>126</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>41</v>
+        <v>298</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>273</v>
+        <v>164</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>173</v>
+        <v>90</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>46</v>
+        <v>258</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J77" s="3">
         <v>1</v>
@@ -4369,184 +4362,182 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>58</v>
+        <v>268</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>294</v>
+        <v>172</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>306</v>
+        <v>52</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>294</v>
+        <v>196</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>51</v>
+        <v>316</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>162</v>
+        <v>321</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>205</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4554,335 +4545,243 @@
         <v>316</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>317</v>
+        <v>182</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>322</v>
+        <v>126</v>
       </c>
       <c r="J85" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>323</v>
+        <v>95</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>325</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>56</v>
+        <v>330</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>236</v>
+        <v>331</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>328</v>
+        <v>47</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
       <c r="J87" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>332</v>
+        <v>172</v>
       </c>
       <c r="J88" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>190</v>
+        <v>337</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>86</v>
+        <v>343</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>330</v>
+        <v>52</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>340</v>
+        <v>164</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>342</v>
+        <v>136</v>
       </c>
       <c r="J91" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J92" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J94" s="3">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J91"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4974,9 +4873,6 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
-    <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4984,8 +4880,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4995,36 +4891,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>164</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5032,277 +4928,239 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>85</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>211</v>
+        <v>293</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>212</v>
+        <v>294</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>213</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>197</v>
+        <v>268</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>221</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C15" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>346</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G16"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5317,8 +5175,6 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5332,47 +5188,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>347</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>292</v>
+        <v>263</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5380,31 +5236,31 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5412,15 +5268,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>157</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5428,23 +5284,23 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>159</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5452,7 +5308,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5471,23 +5327,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5495,31 +5351,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>286</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5527,7 +5383,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5535,7 +5391,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5543,7 +5399,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5551,7 +5407,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5559,7 +5415,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5567,7 +5423,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5575,7 +5431,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5583,7 +5439,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5591,7 +5447,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5605,23 +5461,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
@@ -5629,13 +5485,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3">
-        <v>26.9</v>
+        <v>19.2</v>
       </c>
       <c r="D2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5643,7 +5499,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3">
         <v>15.1</v>
@@ -5657,7 +5513,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3">
         <v>10.9</v>
@@ -5671,7 +5527,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="3">
         <v>6.7</v>
@@ -5685,7 +5541,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
         <v>6.2</v>
@@ -5699,7 +5555,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C7" s="3">
         <v>5.3</v>
@@ -5713,7 +5569,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -5727,13 +5583,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5741,10 +5597,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="C10" s="3">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -5755,13 +5611,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>286</v>
+        <v>128</v>
       </c>
       <c r="C11" s="3">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5769,10 +5625,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="C12" s="3">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -5783,10 +5639,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -5797,13 +5653,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5811,7 +5667,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5825,7 +5681,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5848,46 +5704,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>368</v>
+        <v>322</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>369</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -5903,47 +5759,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5951,7 +5807,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>328</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5959,7 +5815,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5967,7 +5823,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5982,7 +5838,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5994,34 +5850,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6029,31 +5885,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -6061,31 +5917,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4">
@@ -6093,31 +5949,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>322</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
@@ -6125,31 +5981,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>256</v>
+        <v>386</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>391</v>
+        <v>311</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="F5" s="3">
-        <v>76</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>392</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6">
@@ -6157,31 +6013,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F6" s="3">
+        <v>80</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="F6" s="3">
-        <v>76</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="7">
@@ -6189,31 +6045,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>323</v>
+        <v>393</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>324</v>
+        <v>238</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>175</v>
+        <v>394</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F7" s="3">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>173</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8">
@@ -6221,31 +6077,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>400</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>401</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -6253,31 +6109,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F9" s="3">
+        <v>56</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="F9" s="3">
-        <v>57</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="H9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>405</v>
+        <v>327</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>104</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6285,31 +6141,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>333</v>
+        <v>403</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>334</v>
+        <v>238</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>190</v>
+        <v>394</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F10" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>335</v>
+        <v>405</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>281</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
@@ -6317,31 +6173,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="F11" s="3">
         <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12">
@@ -6349,31 +6205,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="F12" s="3">
-        <v>52</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>415</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>322</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -6381,31 +6237,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="F13" s="3">
-        <v>52</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="14">
@@ -6413,31 +6269,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>421</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>324</v>
+        <v>58</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>423</v>
+        <v>64</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>173</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -6445,31 +6301,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>324</v>
+        <v>182</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
@@ -6477,31 +6333,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>284</v>
+        <v>164</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F16" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>207</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -6509,31 +6365,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>144</v>
+        <v>426</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>145</v>
+        <v>257</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>104</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18">
@@ -6541,31 +6397,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F18" s="3">
+        <v>40</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="F18" s="3">
-        <v>47</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>432</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19">
@@ -6573,31 +6429,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>61</v>
+        <v>432</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>433</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>63</v>
+        <v>434</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20">
@@ -6605,31 +6461,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>177</v>
+        <v>436</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21">
@@ -6637,31 +6493,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>90</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W28.xlsx
+++ b/reports/devops-jobs-israel-2026-W28.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="466">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-08T08:41:32</t>
+    <t xml:space="preserve">2026-07-09T10:04:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1%</t>
+    <t xml:space="preserve">2.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -234,1027 +234,1120 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
-    <t xml:space="preserve">Professional Services DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7959680&amp;gh_jid=7959680</t>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Engineer - Berlin / Lisbon / Warsaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1GLOBAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-berlin-lisbon-warsaw-at-1global-4436088167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4434528681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437387394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437309963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4438594459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433127155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4437795960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435227245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36803)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36803-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438235367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4437184121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4434807946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429849553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (Azure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-at-youcc-technologies-ltd-4434842290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarity Sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-clarity-sec-4435649753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/python-infrastructure-engineer-at-infinidat-4435649237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-system-engineer-at-abra-4436065992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-bynet-data-communications-4434831938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4433922741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cyera-4437443238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-reliability-engineer-at-silk-4437161833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-abra-4437772416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-solaredge-technologies-4436952912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - Advanced DIRCM Systems - 236611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-advanced-dircm-systems-236611-at-experis-israel-4433921949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4438218302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437763299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grafana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Professional Services DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Ansible, Docker, CI/CD, Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7597649&amp;gh_jid=7597649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Engineer - Billing Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfraEdge IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infraedge-il-4433786911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4437795960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435227245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437766169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infrastructure Engineer (Linux &amp; AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CloudBuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-linux-aws-at-cloudbuzz-4434817637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4434807946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-at-nvidia-4415716812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Engineer, SRE &amp; LLM Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-engineer-sre-llm-infrastructure-at-confidential-4424224518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration &amp; DevOps Engineer (Kubernetes / OpenShift)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/integration-devops-engineer-kubernetes-openshift-at-commit-4435574441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobgether-4436041571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4433783879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-1006977-at-elad-software-systems-4437184121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer (Databricks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Databricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-databricks-at-quanthealth-4435040714</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-gotfriends-4434530772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4378744789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer | Leading Company (5466)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-leading-company-5466-at-ingima-4438178609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4434528681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MatchPointIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-system-engineer-at-abra-4436065992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vega-In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-architect-at-vega-in-4433188707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-comblack-4436344599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cyera-4437443238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4436064850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-reliability-engineer-at-silk-4437161833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36781)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, GCP, Cloud (any), Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36781-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36792)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36792-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436990743</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
@@ -1275,84 +1368,6 @@
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk and System Administrator (Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Terraform/IaC, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-and-system-administrator-israel-at-zota-4431223683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1365,16 +1380,16 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1526,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -1534,7 +1549,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1542,7 +1557,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1550,7 +1565,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>895</v>
+        <v>915</v>
       </c>
     </row>
     <row r="10">
@@ -1558,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1622,7 +1637,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1630,7 +1645,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1649,20 +1664,20 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -1670,15 +1685,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1686,7 +1701,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1705,31 +1720,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B3" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B4" s="3">
         <v>23</v>
@@ -1737,39 +1752,39 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>449</v>
+        <v>297</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>454</v>
       </c>
       <c r="B9" s="3">
         <v>16</v>
@@ -1777,58 +1792,58 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>350</v>
+        <v>455</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>263</v>
+        <v>354</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1853,13 +1868,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2">
@@ -1867,13 +1882,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1882,88 +1897,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>33.4</v>
+        <v>35.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.0</v>
+        <v>2.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.1</v>
+        <v>30.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>20.0</v>
+        <v>17.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.0</v>
+        <v>14.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1974,9 +1989,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2047,7 +2062,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -2079,7 +2094,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4">
@@ -2111,7 +2126,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -2143,7 +2158,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -2175,7 +2190,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -2207,7 +2222,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -2239,7 +2254,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -2271,7 +2286,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -2288,7 +2303,7 @@
         <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>72</v>
@@ -2303,7 +2318,7 @@
         <v>74</v>
       </c>
       <c r="J10" s="3">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -2311,16 +2326,16 @@
         <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>77</v>
@@ -2332,27 +2347,27 @@
         <v>78</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>80</v>
@@ -2375,7 +2390,7 @@
         <v>83</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>47</v>
@@ -2387,27 +2402,27 @@
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J13" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>47</v>
@@ -2428,18 +2443,18 @@
         <v>89</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J14" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>47</v>
@@ -2451,30 +2466,30 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J15" s="3">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>47</v>
@@ -2483,30 +2498,30 @@
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>47</v>
@@ -2515,30 +2530,30 @@
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>47</v>
@@ -2547,30 +2562,30 @@
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="J18" s="3">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>47</v>
@@ -2579,68 +2594,68 @@
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="J19" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>116</v>
@@ -2655,24 +2670,24 @@
         <v>118</v>
       </c>
       <c r="J21" s="3">
-        <v>51</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>121</v>
@@ -2687,114 +2702,114 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J23" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J25" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>47</v>
@@ -2803,40 +2818,38 @@
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J26" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>144</v>
-      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
@@ -2847,7 +2860,7 @@
         <v>146</v>
       </c>
       <c r="J27" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -2855,10 +2868,10 @@
         <v>147</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>47</v>
@@ -2867,24 +2880,24 @@
         <v>38</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="J28" s="3">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>151</v>
@@ -2893,14 +2906,14 @@
         <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>153</v>
@@ -2909,7 +2922,7 @@
         <v>154</v>
       </c>
       <c r="J29" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2920,7 +2933,7 @@
         <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>47</v>
@@ -2932,60 +2945,60 @@
         <v>157</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="J30" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J31" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>48</v>
@@ -2995,27 +3008,27 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J32" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>48</v>
@@ -3025,27 +3038,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>48</v>
@@ -3055,10 +3068,10 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -3066,13 +3079,13 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>47</v>
@@ -3085,24 +3098,24 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>47</v>
@@ -3115,54 +3128,54 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>47</v>
@@ -3175,24 +3188,24 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="J38" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>47</v>
@@ -3205,10 +3218,10 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J39" s="3">
         <v>45</v>
@@ -3216,16 +3229,16 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>48</v>
@@ -3235,57 +3248,57 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>48</v>
@@ -3295,24 +3308,24 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="J42" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>127</v>
+        <v>202</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>47</v>
@@ -3325,27 +3338,27 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="J43" s="3">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>202</v>
+        <v>47</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>48</v>
@@ -3355,24 +3368,24 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="J44" s="3">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>47</v>
@@ -3385,57 +3398,57 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="J46" s="3">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>48</v>
@@ -3445,13 +3458,13 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3459,10 +3472,10 @@
         <v>52</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>47</v>
@@ -3475,27 +3488,27 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>48</v>
@@ -3505,24 +3518,24 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>90</v>
+        <v>206</v>
       </c>
       <c r="J49" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>218</v>
+        <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>47</v>
@@ -3535,59 +3548,57 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>223</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>79</v>
+        <v>230</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>48</v>
@@ -3597,57 +3608,57 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>227</v>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="J53" s="3">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>48</v>
@@ -3657,24 +3668,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="J54" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>231</v>
+        <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>47</v>
@@ -3687,24 +3698,24 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>234</v>
+        <v>119</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>47</v>
@@ -3717,87 +3728,87 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="J56" s="3">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>238</v>
+        <v>190</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>239</v>
+        <v>152</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="J57" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>242</v>
+        <v>152</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>243</v>
+        <v>47</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="J58" s="3">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>38</v>
@@ -3807,30 +3818,30 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="J59" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
@@ -3840,146 +3851,144 @@
         <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>252</v>
+        <v>206</v>
       </c>
       <c r="J60" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>253</v>
+        <v>71</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="J61" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>191</v>
+        <v>255</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>257</v>
+        <v>162</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>258</v>
+        <v>47</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>260</v>
+        <v>93</v>
       </c>
       <c r="J62" s="3">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>257</v>
+        <v>152</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>258</v>
+        <v>47</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>42</v>
+        <v>260</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>268</v>
+        <v>162</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>48</v>
@@ -3989,116 +3998,114 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>127</v>
+        <v>264</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>270</v>
+        <v>169</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>274</v>
+        <v>152</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>278</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>280</v>
+        <v>189</v>
       </c>
       <c r="J68" s="3">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>281</v>
+        <v>119</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>47</v>
@@ -4111,57 +4118,57 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>184</v>
+        <v>274</v>
       </c>
       <c r="J69" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>283</v>
+        <v>52</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>285</v>
+        <v>152</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>202</v>
+        <v>47</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>287</v>
+        <v>168</v>
       </c>
       <c r="J70" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>288</v>
+        <v>119</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>48</v>
@@ -4171,147 +4178,149 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>291</v>
+        <v>119</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>260</v>
+        <v>159</v>
       </c>
       <c r="J72" s="3">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>294</v>
+        <v>203</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>160</v>
+        <v>249</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>47</v>
+        <v>250</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>164</v>
+        <v>288</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J75" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>127</v>
+        <v>290</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>133</v>
+        <v>250</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>48</v>
@@ -4321,144 +4330,146 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J76" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>52</v>
+        <v>293</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>258</v>
+        <v>47</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>169</v>
+        <v>93</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>306</v>
+        <v>182</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>34</v>
+        <v>299</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>52</v>
+        <v>302</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="J80" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>314</v>
+        <v>187</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>47</v>
@@ -4471,27 +4482,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>172</v>
+        <v>274</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>180</v>
+        <v>307</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>48</v>
@@ -4501,87 +4512,87 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>321</v>
+        <v>152</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>322</v>
+        <v>48</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>182</v>
+        <v>313</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>164</v>
+        <v>314</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>48</v>
+        <v>315</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J84" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>326</v>
+        <v>169</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>210</v>
+        <v>317</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>48</v>
@@ -4591,100 +4602,100 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>126</v>
+        <v>319</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J86" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>164</v>
+        <v>324</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>315</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J87" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>247</v>
+        <v>327</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4692,29 +4703,29 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
@@ -4722,66 +4733,186 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>343</v>
+        <v>168</v>
       </c>
       <c r="J90" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>52</v>
+        <v>335</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J92" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J93" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J91" s="3">
-        <v>26</v>
+      <c r="C94" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J95" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J91"/>
+  <autoFilter ref="A1:J95"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4873,6 +5004,10 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4880,9 +5015,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4914,13 +5049,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4928,18 +5063,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4947,18 +5082,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4966,18 +5101,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4985,18 +5120,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5004,18 +5139,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>288</v>
+        <v>52</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>289</v>
+        <v>224</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5023,18 +5158,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>290</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>293</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5042,18 +5177,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>257</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>268</v>
+        <v>152</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5061,18 +5196,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>314</v>
+        <v>213</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5080,18 +5215,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>316</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5099,18 +5234,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>321</v>
+        <v>162</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5118,18 +5253,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>323</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5137,18 +5272,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>335</v>
+        <v>296</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>336</v>
+        <v>182</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>337</v>
+        <v>59</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5156,11 +5291,144 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>338</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G21"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5175,6 +5443,13 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5188,87 +5463,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>347</v>
+        <v>157</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>263</v>
+        <v>354</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>355</v>
+        <v>149</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
@@ -5276,15 +5551,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>157</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5292,7 +5567,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5300,7 +5575,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5308,7 +5583,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5321,7 +5596,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5330,12 +5605,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5343,15 +5618,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5375,7 +5650,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5383,7 +5658,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5391,7 +5666,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5399,7 +5674,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5407,7 +5682,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5415,7 +5690,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5423,7 +5698,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5431,7 +5706,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5439,7 +5714,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5447,7 +5722,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5468,16 +5743,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
@@ -5485,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C2" s="3">
         <v>19.2</v>
@@ -5499,13 +5774,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3">
-        <v>15.1</v>
+        <v>10.9</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -5513,13 +5788,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="C4" s="3">
-        <v>10.9</v>
+        <v>6.7</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -5527,10 +5802,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -5541,10 +5816,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5555,7 +5830,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C7" s="3">
         <v>5.3</v>
@@ -5569,7 +5844,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C8" s="3">
         <v>5.0</v>
@@ -5597,13 +5872,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="C10" s="3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5611,13 +5886,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5625,10 +5900,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>247</v>
+        <v>182</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -5639,10 +5914,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -5653,13 +5928,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5667,7 +5942,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5681,7 +5956,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5707,18 +5982,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5729,10 +6004,10 @@
         <v>48</v>
       </c>
       <c r="B3" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -5740,10 +6015,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5762,7 +6037,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5770,15 +6045,15 @@
         <v>47</v>
       </c>
       <c r="B2" s="3">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -5791,7 +6066,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5799,7 +6074,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5807,7 +6082,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5815,17 +6090,9 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5838,7 +6105,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5850,10 +6117,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5865,10 +6132,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5885,31 +6152,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>371</v>
+        <v>203</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>59</v>
+        <v>375</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>74</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
@@ -5917,31 +6184,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>191</v>
+        <v>380</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>376</v>
+        <v>200</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
@@ -5949,31 +6216,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>187</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5">
@@ -5981,31 +6248,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>311</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>389</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
@@ -6013,31 +6280,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>225</v>
+        <v>395</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>180</v>
+        <v>396</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7">
@@ -6045,31 +6312,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>393</v>
+        <v>302</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>394</v>
+        <v>152</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F7" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>396</v>
+        <v>305</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>397</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8">
@@ -6077,31 +6344,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>164</v>
+        <v>249</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="F8" s="3">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9">
@@ -6109,31 +6376,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>325</v>
+        <v>394</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F9" s="3">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>327</v>
+        <v>407</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>280</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -6141,31 +6408,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>403</v>
+        <v>290</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>394</v>
+        <v>317</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F10" s="3">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11">
@@ -6173,31 +6440,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>164</v>
+        <v>413</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="F11" s="3">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>389</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
@@ -6205,31 +6472,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>142</v>
+        <v>418</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -6237,31 +6504,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>414</v>
+        <v>213</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>416</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -6269,31 +6536,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>423</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
+        <v>424</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>59</v>
+        <v>222</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>64</v>
+        <v>426</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>65</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15">
@@ -6301,31 +6568,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>74</v>
+        <v>432</v>
       </c>
     </row>
     <row r="16">
@@ -6333,31 +6600,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>422</v>
+        <v>216</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17">
@@ -6365,31 +6632,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>426</v>
+        <v>216</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F17" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18">
@@ -6397,31 +6664,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>200</v>
+        <v>439</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>169</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19">
@@ -6429,31 +6696,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>433</v>
+        <v>134</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="F19" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>169</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -6461,31 +6728,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>178</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21">
@@ -6493,31 +6760,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>439</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>440</v>
+        <v>58</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>442</v>
+        <v>64</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>392</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W28.xlsx
+++ b/reports/devops-jobs-israel-2026-W28.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="478">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-09T10:04:19</t>
+    <t xml:space="preserve">2026-07-10T09:49:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1%</t>
+    <t xml:space="preserve">3.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -147,370 +147,706 @@
     <t xml:space="preserve">2026-05-12</t>
   </si>
   <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, CI/CD, Linux, Python, Bash/Shell, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7709743/?gh_jid=7709743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Architect - DevOps Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Engineer - Berlin / Lisbon / Warsaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1GLOBAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-berlin-lisbon-warsaw-at-1global-4436088167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4434528681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4435945640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437309963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4438646614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4438594459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lead DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, Terraform, CI/CD, Linux, Python, Prometheus, Grafana, CloudFormation, CDK, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4767279101?gh_jid=4767279101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, CI/CD, Linux, Python, Bash/Shell, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7709743/?gh_jid=7709743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobgether-4436041571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPE Aruba Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlgoSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4438868943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36803)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36803-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438235367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4437184121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4435684493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchPointIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
     <t xml:space="preserve">Site Reliability Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Linux, Python, Prometheus, Grafana, New Relic, Networking, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7957880&amp;gh_jid=7957880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4684943006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668077006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Architect - DevOps Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Networking, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668071006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Kafka, Networking, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8426614002?gh_jid=8426614002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Engineer - Billing Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python, Postgres, Redis, Kafka, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer - Berlin / Lisbon / Warsaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1GLOBAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-berlin-lisbon-warsaw-at-1global-4436088167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4434528681</t>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4434807946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
@@ -522,64 +858,7 @@
     <t xml:space="preserve">Yizra'el, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437387394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437309963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4438594459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433127155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPE Aruba Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
   </si>
   <si>
     <t xml:space="preserve">Paragon</t>
@@ -588,18 +867,48 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
+    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (Azure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-at-youcc-technologies-ltd-4434842290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-logica-it-4434847048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sr. DevOps Engineer</t>
   </si>
   <si>
@@ -615,781 +924,508 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-27</t>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Facing System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarity Sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4435649753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/python-infrastructure-engineer-at-infinidat-4435649237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-system-engineer-at-abra-4436065992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4433922741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cyera-4437443238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-reliability-engineer-at-silk-4437161833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-abra-4437772416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-ai-4435948577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
   </si>
   <si>
     <t xml:space="preserve">Nogamy</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4437795960</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-audiocodes-4435227245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36803)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36803-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438235367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ycon | DevOps &amp; ALM Services LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-devops-engineer-at-ycon-devops-alm-services-ltd-4434518026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4437184121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4406062787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-bmc-software-4418686351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4427516055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4434807946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429849553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dropit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (Azure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-at-youcc-technologies-ltd-4434842290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437763299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Clarity Sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-clarity-sec-4435649753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/python-infrastructure-engineer-at-infinidat-4435649237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-system-engineer-at-abra-4436065992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-bynet-data-communications-4434831938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4433922741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cyera-4437443238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-reliability-engineer-at-silk-4437161833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-abra-4437772416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-solaredge-technologies-4436952912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer - Advanced DIRCM Systems - 236611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-advanced-dircm-systems-236611-at-experis-israel-4433921949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENECIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4438218302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437763299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grafana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Operations Engineer</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
     <t xml:space="preserve">Confidential Careers</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-calanit-by-one-4433302441</t>
+    <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-gotfriends-4434530772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36781)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, GCP, Cloud (any), Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36781-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436995599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36792)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36792-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4436990743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1541,7 +1577,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
@@ -1549,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1557,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1565,7 +1601,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>915</v>
+        <v>924</v>
       </c>
     </row>
     <row r="10">
@@ -1573,7 +1609,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1637,7 +1673,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -1645,7 +1681,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1664,7 +1700,7 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
@@ -1672,23 +1708,23 @@
         <v>403</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1701,7 +1737,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1720,130 +1756,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B3" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>452</v>
+        <v>343</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>358</v>
+        <v>465</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>467</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>455</v>
+        <v>366</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1868,13 +1904,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2">
@@ -1882,13 +1918,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>13.4</v>
+        <v>26.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1897,88 +1933,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3">
-        <v>35.8</v>
+        <v>33.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.1</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.9</v>
+        <v>38.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.5</v>
+        <v>24.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>14.5</v>
+        <v>21.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2062,7 +2098,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -2070,63 +2106,63 @@
         <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -2134,80 +2170,80 @@
         <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>60</v>
@@ -2219,103 +2255,103 @@
         <v>61</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>58</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J10" s="3">
         <v>29</v>
@@ -2323,16 +2359,16 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>38</v>
@@ -2350,39 +2386,39 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J12" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -2390,13 +2426,13 @@
         <v>83</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>38</v>
@@ -2414,7 +2450,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -2422,109 +2458,109 @@
         <v>87</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J15" s="3">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="J16" s="3">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>38</v>
@@ -2542,21 +2578,21 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>38</v>
@@ -2571,477 +2607,473 @@
         <v>107</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J19" s="3">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J21" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J23" s="3">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>136</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J25" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>135</v>
+        <v>44</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="J26" s="3">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="G27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J27" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>149</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="J28" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>157</v>
-      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="J30" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -3049,106 +3081,106 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="J35" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="J36" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>38</v>
@@ -3158,10 +3190,10 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="J37" s="3">
         <v>4</v>
@@ -3169,109 +3201,109 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J39" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="J40" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
@@ -3281,204 +3313,204 @@
         <v>197</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="J41" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="J44" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="J45" s="3">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>38</v>
@@ -3488,87 +3520,87 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J48" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>222</v>
+        <v>155</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>218</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>226</v>
+        <v>49</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3578,57 +3610,57 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="J51" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>230</v>
+        <v>112</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>206</v>
+        <v>149</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>38</v>
@@ -3638,57 +3670,57 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="J53" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>119</v>
+        <v>230</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>222</v>
+        <v>146</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3698,60 +3730,60 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>119</v>
+        <v>236</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>162</v>
+        <v>228</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
@@ -3761,97 +3793,97 @@
         <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="J57" s="3">
-        <v>46</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="J58" s="3">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>128</v>
+        <v>249</v>
       </c>
       <c r="J59" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>52</v>
+        <v>250</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="J60" s="3">
         <v>2</v>
@@ -3859,46 +3891,46 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>71</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3908,147 +3940,147 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="J62" s="3">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>168</v>
+        <v>263</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="J65" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J66" s="3">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>38</v>
@@ -4058,811 +4090,813 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>270</v>
+        <v>112</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>152</v>
+        <v>274</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="J68" s="3">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>119</v>
+        <v>276</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>162</v>
+        <v>278</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>274</v>
+        <v>158</v>
       </c>
       <c r="J69" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>168</v>
+        <v>269</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>119</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>277</v>
+        <v>180</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>119</v>
+        <v>284</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F72" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>266</v>
+        <v>158</v>
       </c>
       <c r="J73" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>162</v>
+        <v>292</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>63</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>286</v>
+        <v>112</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>288</v>
+        <v>146</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="J75" s="3">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>293</v>
+        <v>49</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="J77" s="3">
-        <v>55</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>297</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>302</v>
+        <v>159</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>187</v>
+        <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="J81" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>306</v>
+        <v>177</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>307</v>
+        <v>56</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F82" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>314</v>
+        <v>146</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>169</v>
+        <v>322</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>319</v>
+        <v>149</v>
       </c>
       <c r="J85" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>320</v>
+        <v>146</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>323</v>
+        <v>165</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="J87" s="3">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>59</v>
+        <v>333</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>38</v>
+        <v>156</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>38</v>
+        <v>156</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>335</v>
+        <v>112</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>87</v>
+        <v>342</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>152</v>
+        <v>333</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>343</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="J92" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>341</v>
+        <v>237</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>152</v>
+        <v>345</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>192</v>
+        <v>330</v>
       </c>
       <c r="J93" s="3">
-        <v>46</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>345</v>
+        <v>146</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>38</v>
@@ -4872,47 +4906,137 @@
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>347</v>
+        <v>112</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J95" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J96" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J97" s="3">
         <v>1</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J98" s="3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J95"/>
+  <autoFilter ref="A1:J98"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5008,6 +5132,9 @@
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5015,9 +5142,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="1" max="1" width="53" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5049,13 +5176,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5063,18 +5190,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5082,18 +5209,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5101,18 +5228,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5120,18 +5247,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>215</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5139,18 +5266,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>276</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>152</v>
+        <v>278</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5158,18 +5285,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>52</v>
+        <v>282</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>238</v>
+        <v>180</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5177,18 +5304,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5196,18 +5323,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>162</v>
+        <v>333</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5215,220 +5342,11 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B21" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>346</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5439,17 +5357,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5463,127 +5370,127 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>149</v>
+        <v>343</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>360</v>
+        <v>142</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5596,7 +5503,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5605,12 +5512,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5618,7 +5525,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3">
         <v>3</v>
@@ -5626,7 +5533,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5634,15 +5541,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5650,7 +5557,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5658,7 +5565,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5666,7 +5573,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5674,7 +5581,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5682,7 +5589,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5690,7 +5597,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5698,7 +5605,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5706,7 +5613,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5714,7 +5621,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5722,7 +5629,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5736,23 +5643,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5760,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3">
         <v>19.2</v>
@@ -5774,7 +5681,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3">
         <v>10.9</v>
@@ -5788,7 +5695,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C4" s="3">
         <v>6.7</v>
@@ -5802,10 +5709,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="C5" s="3">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -5816,10 +5723,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="C6" s="3">
-        <v>5.8</v>
+        <v>5.0</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5830,10 +5737,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5844,13 +5751,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="C8" s="3">
-        <v>5.0</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5858,13 +5765,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="C9" s="3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5872,13 +5779,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>169</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5886,10 +5793,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="C11" s="3">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -5900,7 +5807,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C12" s="3">
         <v>3.1</v>
@@ -5914,7 +5821,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3">
         <v>2.9</v>
@@ -5928,7 +5835,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C14" s="3">
         <v>2.6</v>
@@ -5942,7 +5849,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5956,7 +5863,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5982,18 +5889,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>315</v>
+        <v>156</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -6001,13 +5908,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3">
         <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4">
@@ -6015,10 +5922,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -6037,23 +5944,23 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -6066,7 +5973,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6074,7 +5981,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6082,7 +5989,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6090,9 +5997,17 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>144</v>
+        <v>299</v>
       </c>
       <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6105,7 +6020,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6117,10 +6032,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6132,10 +6047,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6152,31 +6067,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>203</v>
+        <v>385</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>375</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>189</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3">
@@ -6184,31 +6099,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>380</v>
+        <v>304</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>200</v>
+        <v>391</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>154</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4">
@@ -6216,31 +6131,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>389</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5">
@@ -6248,31 +6163,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>391</v>
+        <v>280</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>192</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
@@ -6280,31 +6195,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>396</v>
+        <v>191</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>399</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -6312,31 +6227,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F7" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>305</v>
+        <v>408</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
@@ -6344,31 +6259,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>103</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6376,31 +6291,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>252</v>
+        <v>413</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F9" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -6408,31 +6323,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>290</v>
+        <v>416</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>169</v>
+        <v>417</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>317</v>
+        <v>418</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="F10" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>410</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -6440,31 +6355,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>413</v>
+        <v>146</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="F11" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>154</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -6472,13 +6387,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>386</v>
@@ -6487,16 +6402,16 @@
         <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -6504,31 +6419,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>213</v>
+        <v>431</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="F13" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>154</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14">
@@ -6536,31 +6451,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>222</v>
+        <v>146</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="F14" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15">
@@ -6568,31 +6483,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="F15" s="3">
         <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16">
@@ -6600,31 +6515,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>159</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -6632,31 +6547,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>436</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>437</v>
+        <v>61</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -6664,31 +6579,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>403</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>442</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -6696,31 +6611,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>280</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>403</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>93</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20">
@@ -6728,31 +6643,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>445</v>
+        <v>209</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>403</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>447</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
@@ -6760,31 +6675,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>62</v>
+        <v>457</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>59</v>
+        <v>458</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>64</v>
+        <v>460</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W28.xlsx
+++ b/reports/devops-jobs-israel-2026-W28.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-10T09:49:55</t>
+    <t xml:space="preserve">2026-07-12T08:28:52</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1%</t>
+    <t xml:space="preserve">2.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -471,51 +471,51 @@
     <t xml:space="preserve">2026-07-06</t>
   </si>
   <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4435945640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamelio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4434528681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agora</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-agora-4437799472</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4438643241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamelio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-chamelio-4434528681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4435945640</t>
-  </si>
-  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
@@ -525,6 +525,36 @@
     <t xml:space="preserve">2026-07-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobgether-4436041571</t>
+  </si>
+  <si>
     <t xml:space="preserve">comblack</t>
   </si>
   <si>
@@ -534,13 +564,82 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4438646614</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
+    <t xml:space="preserve">Directeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4428998732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogamy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4437795960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
   </si>
   <si>
     <t xml:space="preserve">DataTeam</t>
@@ -552,22 +651,265 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4438594459</t>
   </si>
   <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4433787217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobgether-4436041571</t>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incredibuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataspan.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-dataspan-ai-4438322775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4437184121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnTarget Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kadima, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437759387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-devops-engineer-at-jobscroller-4438924143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineering Group Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineering-group-tech-lead-at-monday-com-4430704843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer (CloudOps) - Production</t>
@@ -579,19 +921,106 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloudops-production-at-hpe-aruba-networking-4438248995</t>
   </si>
   <si>
-    <t xml:space="preserve">Dropit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dropit-4433950725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AlgoSec</t>
+    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer (Agentic Workflows)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corephotonics Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-agentic-workflows-at-corephotonics-ltd-4437212081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobscroller-4438942609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-logica-it-4434847048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-data-platform-engineer-at-medulla-4437152019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cato-networks-4427845609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4378744789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36803)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36803-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438235367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmeq, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-kla-4415281953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - CAS (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-cas-cortex-cloud-at-palo-alto-networks-4416832982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Facing System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarity Sec</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
@@ -600,654 +1029,246 @@
     <t xml:space="preserve">Petah Tikva</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-israel-at-algosec-4438868943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36803)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36803-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4438235367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-matrix-4433934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-buildots-4433951942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4438271470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-natural-intelligence-4425622056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4433945136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-descope-4431665949</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4435649753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENECIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-genecit-4436692890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer - Advanced DIRCM Systems - 236611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-advanced-dircm-systems-236611-at-experis-israel-4433921949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4437215091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-ai-4435948577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4434549295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-coralogix-4431747155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Engineer (1006977)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4437184121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4435684493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4433942368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-pipl-4437165719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MatchPointIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matchpointit-4436991278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4434807946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-gotfriends-4434843227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incredibuild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-incredibuild-4425732730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaaS Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/saas-site-reliability-engineer-at-bmc-software-4418678492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Microsoft Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-microsoft-cloud-engineer-at-jobgether-4437987101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer (Azure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-at-youcc-technologies-ltd-4434842290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-logica-it-4434847048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Infra/cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infra-cloud-engineer-at-applied-materials-israel-4429415734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-alice-formerly-activefence-4412768277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client Facing System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarity Sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4435649753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/python-infrastructure-engineer-at-infinidat-4435649237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-system-engineer-at-abra-4436065992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4433922741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-cyera-4437443238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-reliability-engineer-at-silk-4437161833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-abra-4437772416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-directeam-4433792633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Linux Infrastructure and Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-linux-infrastructure-and-automation-engineer-at-nvidia-ai-4435948577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375563419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogamy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nogamy-4437795960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Team Leader (Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnTarget Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-team-leader-cloud-at-ontarget-communications-4437763299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4434818632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-engineer-at-sela-4428931319</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -1260,169 +1281,136 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-confidential-careers-4434832851</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
   </si>
   <si>
     <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
+    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
@@ -1577,7 +1565,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -1585,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1593,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1601,7 +1589,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>924</v>
+        <v>936</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1597,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1673,7 +1661,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1700,36 +1688,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1756,31 +1744,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B2" s="3">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B4" s="3">
         <v>27</v>
@@ -1788,7 +1776,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>343</v>
+        <v>460</v>
       </c>
       <c r="B5" s="3">
         <v>25</v>
@@ -1796,47 +1784,47 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B6" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>465</v>
+        <v>353</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>315</v>
+        <v>462</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>467</v>
+        <v>372</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3">
         <v>12</v>
@@ -1844,42 +1832,42 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>468</v>
+        <v>366</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>363</v>
+        <v>464</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1904,13 +1892,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2">
@@ -1921,10 +1909,10 @@
         <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>26.0</v>
+        <v>13.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1933,88 +1921,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
-        <v>33.8</v>
+        <v>37.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>8.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>38.7</v>
+        <v>30.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>24.5</v>
+        <v>21.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.3</v>
+        <v>15.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2026,7 +2014,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2098,7 +2086,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -2130,7 +2118,7 @@
         <v>48</v>
       </c>
       <c r="J3" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -2162,7 +2150,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -2194,7 +2182,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -2226,7 +2214,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -2258,7 +2246,7 @@
         <v>62</v>
       </c>
       <c r="J7" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -2290,7 +2278,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -2322,7 +2310,7 @@
         <v>72</v>
       </c>
       <c r="J9" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -2354,7 +2342,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -2386,7 +2374,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -2418,7 +2406,7 @@
         <v>72</v>
       </c>
       <c r="J12" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -2450,7 +2438,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -2482,7 +2470,7 @@
         <v>92</v>
       </c>
       <c r="J14" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -2514,7 +2502,7 @@
         <v>96</v>
       </c>
       <c r="J15" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -2546,7 +2534,7 @@
         <v>79</v>
       </c>
       <c r="J16" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -2578,7 +2566,7 @@
         <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -2610,7 +2598,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -2642,7 +2630,7 @@
         <v>111</v>
       </c>
       <c r="J19" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2674,7 +2662,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -2706,7 +2694,7 @@
         <v>121</v>
       </c>
       <c r="J21" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -2738,7 +2726,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -2770,7 +2758,7 @@
         <v>131</v>
       </c>
       <c r="J23" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -2802,7 +2790,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
@@ -2832,7 +2820,7 @@
         <v>139</v>
       </c>
       <c r="J25" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -2864,7 +2852,7 @@
         <v>79</v>
       </c>
       <c r="J26" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27">
@@ -2896,7 +2884,7 @@
         <v>149</v>
       </c>
       <c r="J27" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -2907,10 +2895,10 @@
         <v>150</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>45</v>
@@ -2920,10 +2908,10 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J28" s="3">
         <v>2</v>
@@ -2931,19 +2919,19 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
@@ -2956,7 +2944,7 @@
         <v>158</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2967,23 +2955,23 @@
         <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J30" s="3">
         <v>2</v>
@@ -2994,13 +2982,13 @@
         <v>112</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>45</v>
@@ -3016,7 +3004,7 @@
         <v>158</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -3027,7 +3015,7 @@
         <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>37</v>
@@ -3046,7 +3034,7 @@
         <v>167</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3057,10 +3045,10 @@
         <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>45</v>
@@ -3070,24 +3058,24 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>44</v>
@@ -3095,113 +3083,115 @@
       <c r="E34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="G34" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="J34" s="3">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>149</v>
       </c>
       <c r="J37" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>184</v>
@@ -3223,10 +3213,10 @@
         <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -3234,13 +3224,13 @@
         <v>112</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>45</v>
@@ -3250,54 +3240,54 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>118</v>
@@ -3310,24 +3300,24 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>44</v>
@@ -3340,13 +3330,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="J42" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3354,10 +3344,10 @@
         <v>112</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>44</v>
@@ -3370,43 +3360,43 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="J43" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>167</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -3414,10 +3404,10 @@
         <v>112</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>44</v>
@@ -3430,43 +3420,43 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>206</v>
+        <v>149</v>
       </c>
       <c r="J45" s="3">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="J46" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
@@ -3474,10 +3464,10 @@
         <v>112</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>44</v>
@@ -3490,13 +3480,13 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J47" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -3504,7 +3494,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>146</v>
@@ -3520,81 +3510,81 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="J48" s="3">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>214</v>
+        <v>112</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="J49" s="3">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>49</v>
+        <v>226</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>146</v>
@@ -3603,17 +3593,17 @@
         <v>44</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="J51" s="3">
         <v>0</v>
@@ -3621,16 +3611,16 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>112</v>
+        <v>230</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>45</v>
@@ -3640,57 +3630,59 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F53" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>44</v>
+        <v>240</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>45</v>
@@ -3700,27 +3692,27 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J54" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>49</v>
+        <v>242</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3730,81 +3722,81 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>174</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="J56" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>49</v>
+        <v>248</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>242</v>
+        <v>44</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="J57" s="3">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>49</v>
+        <v>251</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>146</v>
@@ -3820,84 +3812,84 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="J59" s="3">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>44</v>
@@ -3910,84 +3902,84 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="J61" s="3">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>155</v>
+        <v>267</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>165</v>
+        <v>252</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>44</v>
@@ -4000,13 +3992,13 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="J64" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -4014,10 +4006,10 @@
         <v>112</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>44</v>
@@ -4030,70 +4022,70 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="J65" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>266</v>
+        <v>49</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>44</v>
+        <v>240</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="J66" s="3">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>210</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="J67" s="3">
         <v>3</v>
@@ -4104,10 +4096,10 @@
         <v>112</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>274</v>
+        <v>156</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>44</v>
@@ -4120,87 +4112,87 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>173</v>
+        <v>280</v>
       </c>
       <c r="J68" s="3">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>276</v>
+        <v>49</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>278</v>
+        <v>146</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>112</v>
+        <v>283</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>269</v>
+        <v>86</v>
       </c>
       <c r="J70" s="3">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>282</v>
+        <v>52</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>38</v>
@@ -4210,53 +4202,51 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>155</v>
+        <v>290</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>146</v>
@@ -4265,34 +4255,34 @@
         <v>44</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>290</v>
+        <v>112</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>292</v>
+        <v>156</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>45</v>
@@ -4302,21 +4292,21 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>294</v>
+        <v>203</v>
       </c>
       <c r="J74" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>112</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>146</v>
@@ -4332,51 +4322,51 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="J75" s="3">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>297</v>
+        <v>187</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>298</v>
+        <v>188</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>299</v>
+        <v>118</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>249</v>
+        <v>190</v>
       </c>
       <c r="J76" s="3">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>146</v>
@@ -4392,24 +4382,24 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>44</v>
@@ -4422,30 +4412,30 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>175</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>228</v>
+        <v>176</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
@@ -4455,48 +4445,48 @@
         <v>308</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="J79" s="3">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>246</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>159</v>
+        <v>310</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>146</v>
@@ -4505,66 +4495,64 @@
         <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="J81" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F82" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="G82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="I82" s="3" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>45</v>
@@ -4574,27 +4562,27 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="D84" s="3" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>45</v>
@@ -4607,21 +4595,21 @@
         <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>206</v>
+        <v>322</v>
       </c>
       <c r="J84" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>323</v>
+        <v>198</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>118</v>
@@ -4634,27 +4622,27 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>146</v>
+        <v>328</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>45</v>
@@ -4664,87 +4652,87 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>165</v>
+        <v>252</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>328</v>
+        <v>146</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>330</v>
+        <v>229</v>
       </c>
       <c r="J87" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>118</v>
+        <v>335</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J88" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>318</v>
+        <v>184</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>335</v>
+        <v>146</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>45</v>
@@ -4754,57 +4742,57 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J90" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>112</v>
+        <v>342</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>45</v>
@@ -4814,59 +4802,57 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="J91" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>343</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>45</v>
@@ -4876,57 +4862,59 @@
         <v>23</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>330</v>
+        <v>229</v>
       </c>
       <c r="J93" s="3">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>347</v>
+        <v>150</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>146</v>
+        <v>350</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="G94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="J94" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>112</v>
+        <v>355</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>349</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>118</v>
+        <v>240</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>45</v>
@@ -4936,107 +4924,79 @@
         <v>23</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="J95" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="J96" s="3">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>355</v>
+        <v>215</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>356</v>
+        <v>156</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>299</v>
+        <v>44</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F97" s="3"/>
+      <c r="F97" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="G97" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="J97" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J98" s="3">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J98"/>
+  <autoFilter ref="A1:J97"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5134,7 +5094,6 @@
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5142,9 +5101,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="53" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5176,13 +5135,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>154</v>
+        <v>227</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5190,18 +5149,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5209,18 +5168,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>164</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>169</v>
+        <v>244</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5228,18 +5187,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>170</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>190</v>
+        <v>246</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5247,15 +5206,15 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>193</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>146</v>
@@ -5266,18 +5225,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>278</v>
+        <v>156</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5285,18 +5244,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5304,18 +5263,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>146</v>
+        <v>328</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5323,18 +5282,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>289</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>162</v>
+        <v>252</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>333</v>
+        <v>146</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5342,11 +5301,68 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>344</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5357,6 +5373,9 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5370,10 +5389,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
@@ -5381,12 +5400,12 @@
         <v>147</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -5394,7 +5413,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B4" s="3">
         <v>15</v>
@@ -5402,7 +5421,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5410,15 +5429,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -5426,15 +5445,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5442,7 +5461,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -5450,7 +5469,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="B11" s="3">
         <v>9</v>
@@ -5458,10 +5477,10 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -5474,7 +5493,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5482,7 +5501,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -5490,7 +5509,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5503,7 +5522,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5512,7 +5531,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5533,7 +5552,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -5541,7 +5560,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5589,7 +5608,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5597,7 +5616,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5605,7 +5624,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5613,7 +5632,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5621,7 +5640,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5629,7 +5648,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5643,23 +5662,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5751,10 +5770,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="C8" s="3">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="D8" s="3">
         <v>3</v>
@@ -5765,13 +5784,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>237</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5779,13 +5798,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>252</v>
       </c>
       <c r="C10" s="3">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5793,7 +5812,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C11" s="3">
         <v>3.1</v>
@@ -5807,13 +5826,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="C12" s="3">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5821,13 +5840,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5835,13 +5854,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5849,13 +5868,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5863,7 +5882,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5889,18 +5908,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5911,10 +5930,10 @@
         <v>45</v>
       </c>
       <c r="B3" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4">
@@ -5922,10 +5941,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -5944,7 +5963,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -5952,7 +5971,7 @@
         <v>44</v>
       </c>
       <c r="B2" s="3">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -5960,7 +5979,7 @@
         <v>118</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -5973,7 +5992,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5981,15 +6000,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>240</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5997,7 +6016,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>299</v>
+        <v>194</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -6005,7 +6024,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>242</v>
+        <v>335</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6032,10 +6051,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6047,10 +6066,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6067,31 +6086,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -6099,13 +6118,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>390</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>304</v>
+        <v>201</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>391</v>
+        <v>213</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>392</v>
@@ -6120,10 +6139,10 @@
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>394</v>
+        <v>214</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>269</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4">
@@ -6131,31 +6150,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>397</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
@@ -6163,31 +6182,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>320</v>
+        <v>399</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>321</v>
+        <v>402</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>121</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
@@ -6195,31 +6214,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F6" s="3">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
@@ -6227,31 +6246,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>251</v>
+        <v>408</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>196</v>
+        <v>334</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F7" s="3">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>217</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -6259,31 +6278,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>165</v>
+        <v>412</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>328</v>
+        <v>198</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F8" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6291,31 +6310,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>413</v>
+        <v>165</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>196</v>
+        <v>267</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F9" s="3">
         <v>76</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>167</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10">
@@ -6323,19 +6342,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>417</v>
+        <v>395</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>418</v>
+        <v>198</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="F10" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>420</v>
@@ -6347,7 +6366,7 @@
         <v>421</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
@@ -6355,31 +6374,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F11" s="3">
+        <v>76</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F11" s="3">
-        <v>68</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>92</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12">
@@ -6387,31 +6406,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>146</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -6419,31 +6438,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F13" s="3">
+        <v>57</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F13" s="3">
-        <v>56</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>433</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>434</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
@@ -6451,31 +6470,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15">
@@ -6483,31 +6502,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>441</v>
+        <v>127</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>444</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -6515,31 +6534,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>127</v>
+        <v>437</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F16" s="3">
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>86</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17">
@@ -6547,31 +6566,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>59</v>
+        <v>440</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
+        <v>441</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>61</v>
+        <v>443</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>62</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18">
@@ -6579,31 +6598,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F18" s="3">
+        <v>47</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F18" s="3">
-        <v>44</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>451</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -6611,31 +6630,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>452</v>
+        <v>59</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>280</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="F19" s="3">
         <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>454</v>
+        <v>61</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>389</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -6643,31 +6662,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>86</v>
+        <v>391</v>
       </c>
     </row>
     <row r="21">
@@ -6675,31 +6694,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>237</v>
+        <v>454</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>458</v>
+        <v>56</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
